--- a/exports/trend_1d/BDL_full_report.xlsx
+++ b/exports/trend_1d/BDL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>10.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H2" t="n">
-        <v>190.2</v>
+        <v>185.45</v>
       </c>
       <c r="I2" t="n">
         <v>186.00085591517</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.17</v>
+        <v>-3.64</v>
       </c>
       <c r="L2" t="n">
-        <v>3.27</v>
+        <v>3.87</v>
       </c>
       <c r="M2" t="n">
         <v>1.8</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>7.78</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43248</v>
+        <v>43249</v>
       </c>
       <c r="H3" t="n">
-        <v>198.1</v>
+        <v>201.3</v>
       </c>
       <c r="I3" t="n">
         <v>198.2469228792712</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.82</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>7.55</v>
+        <v>10.92</v>
       </c>
       <c r="M3" t="n">
         <v>0.4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.89</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43272</v>
+        <v>43273</v>
       </c>
       <c r="H4" t="n">
-        <v>191.1</v>
+        <v>190.35</v>
       </c>
       <c r="I4" t="n">
         <v>190.775171141075</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.07</v>
+        <v>-5.44</v>
       </c>
       <c r="L4" t="n">
-        <v>5.27</v>
+        <v>5.86</v>
       </c>
       <c r="M4" t="n">
         <v>0.98</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.97</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H5" t="n">
-        <v>171.2</v>
+        <v>187.85</v>
       </c>
       <c r="I5" t="n">
         <v>184.8920706679014</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K5" t="n">
-        <v>10.06</v>
+        <v>1.31</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
@@ -726,7 +785,7 @@
         <v>1.86</v>
       </c>
       <c r="N5" t="n">
-        <v>2.38</v>
+        <v>9.73</v>
       </c>
       <c r="O5" t="n">
         <v>-0.39</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>13.32</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43348</v>
+        <v>43349</v>
       </c>
       <c r="H6" t="n">
-        <v>174.3</v>
+        <v>172.8</v>
       </c>
       <c r="I6" t="n">
         <v>173.3100398221798</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.21</v>
+        <v>-8.01</v>
       </c>
       <c r="L6" t="n">
-        <v>8.94</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>1.56</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.33</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H7" t="n">
-        <v>144.1</v>
+        <v>159.05</v>
       </c>
       <c r="I7" t="n">
         <v>151.5766192862138</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K7" t="n">
-        <v>16.61</v>
+        <v>7.96</v>
       </c>
       <c r="L7" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>3.62</v>
+        <v>4.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.94</v>
+        <v>10.37</v>
       </c>
       <c r="O7" t="n">
         <v>-0.86</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>14.63</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43440</v>
+        <v>43441</v>
       </c>
       <c r="H8" t="n">
-        <v>137.55</v>
+        <v>135.4</v>
       </c>
       <c r="I8" t="n">
         <v>135.787871389993</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>-13.52</v>
+        <v>-14.87</v>
       </c>
       <c r="L8" t="n">
-        <v>14.18</v>
+        <v>15.12</v>
       </c>
       <c r="M8" t="n">
         <v>2.23</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>10.97</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43472</v>
+        <v>43473</v>
       </c>
       <c r="H9" t="n">
-        <v>139.2</v>
+        <v>148.8</v>
       </c>
       <c r="I9" t="n">
         <v>145.4760066367367</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.81</v>
+        <v>-9.9</v>
       </c>
       <c r="L9" t="n">
-        <v>6.39</v>
+        <v>18.21</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>6.9</v>
       </c>
       <c r="O9" t="n">
         <v>-1.56</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.91</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H10" t="n">
-        <v>134.9</v>
+        <v>131.8</v>
       </c>
       <c r="I10" t="n">
         <v>132.5716436770197</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.34</v>
+        <v>-11.42</v>
       </c>
       <c r="L10" t="n">
-        <v>9.91</v>
+        <v>12.16</v>
       </c>
       <c r="M10" t="n">
         <v>1.31</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>13.71</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43522</v>
+        <v>43523</v>
       </c>
       <c r="H11" t="n">
-        <v>125.75</v>
+        <v>145.4</v>
       </c>
       <c r="I11" t="n">
         <v>130.5843679321679</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K11" t="n">
-        <v>4.59</v>
+        <v>-10.32</v>
       </c>
       <c r="L11" t="n">
-        <v>4.86</v>
+        <v>11.91</v>
       </c>
       <c r="M11" t="n">
         <v>11.01</v>
       </c>
       <c r="N11" t="n">
-        <v>6.39</v>
+        <v>15.63</v>
       </c>
       <c r="O11" t="n">
         <v>-2.3</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>21.44</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H12" t="n">
-        <v>141.3</v>
+        <v>139.15</v>
       </c>
       <c r="I12" t="n">
         <v>140.2263024366913</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.82</v>
+        <v>-4.3</v>
       </c>
       <c r="L12" t="n">
         <v>14.17</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.41</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H13" t="n">
-        <v>131.9</v>
+        <v>146.9</v>
       </c>
       <c r="I13" t="n">
         <v>142.4866073410473</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>5.21</v>
+        <v>-5.57</v>
       </c>
       <c r="L13" t="n">
-        <v>4.81</v>
+        <v>13.55</v>
       </c>
       <c r="M13" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4.14</v>
+        <v>11.37</v>
       </c>
       <c r="O13" t="n">
         <v>-1.52</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>14.84</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43623</v>
+        <v>43626</v>
       </c>
       <c r="H14" t="n">
-        <v>145.3</v>
+        <v>142.75</v>
       </c>
       <c r="I14" t="n">
         <v>144.4269613385338</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.09</v>
+        <v>-2.83</v>
       </c>
       <c r="L14" t="n">
         <v>9.09</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>15.43</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43643</v>
+        <v>43644</v>
       </c>
       <c r="H15" t="n">
-        <v>157.25</v>
+        <v>169.9</v>
       </c>
       <c r="I15" t="n">
         <v>164.7701630205735</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.16</v>
+        <v>-19.02</v>
       </c>
       <c r="L15" t="n">
-        <v>13.06</v>
+        <v>19.75</v>
       </c>
       <c r="M15" t="n">
         <v>1.15</v>
       </c>
       <c r="N15" t="n">
-        <v>7.12</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O15" t="n">
         <v>-1.75</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>15.92</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H16" t="n">
-        <v>159</v>
+        <v>148.9</v>
       </c>
       <c r="I16" t="n">
         <v>149.2667106001662</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.42</v>
+        <v>-12.36</v>
       </c>
       <c r="L16" t="n">
-        <v>7.3</v>
+        <v>13.18</v>
       </c>
       <c r="M16" t="n">
         <v>1.68</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>6.35</v>
       </c>
       <c r="O16" t="n">
         <v>8.039999999999999</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>17.73</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43731</v>
+        <v>43732</v>
       </c>
       <c r="H17" t="n">
-        <v>151.1</v>
+        <v>155.25</v>
       </c>
       <c r="I17" t="n">
         <v>152.8619941266029</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.48</v>
+        <v>-4.26</v>
       </c>
       <c r="L17" t="n">
         <v>6.72</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>12.49</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43748</v>
+        <v>43749</v>
       </c>
       <c r="H18" t="n">
-        <v>141.6</v>
+        <v>140.9</v>
       </c>
       <c r="I18" t="n">
         <v>141.3864626545746</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.24</v>
       </c>
       <c r="L18" t="n">
-        <v>9.18</v>
+        <v>9.66</v>
       </c>
       <c r="M18" t="n">
         <v>0.92</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>11.86</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H19" t="n">
-        <v>151.4</v>
+        <v>163.9</v>
       </c>
       <c r="I19" t="n">
         <v>152.9725084805826</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.45</v>
+        <v>-16.32</v>
       </c>
       <c r="L19" t="n">
-        <v>7.84</v>
+        <v>20.48</v>
       </c>
       <c r="M19" t="n">
         <v>1.21</v>
       </c>
       <c r="N19" t="n">
-        <v>2.35</v>
+        <v>8.26</v>
       </c>
       <c r="O19" t="n">
         <v>-0.49</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>13.39</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H20" t="n">
-        <v>153.9</v>
+        <v>150.5</v>
       </c>
       <c r="I20" t="n">
         <v>153.4995303236232</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.1</v>
+        <v>-8.18</v>
       </c>
       <c r="L20" t="n">
-        <v>8.02</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>1.49</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>15.54</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43843</v>
+        <v>43844</v>
       </c>
       <c r="H21" t="n">
-        <v>151.8</v>
+        <v>157.5</v>
       </c>
       <c r="I21" t="n">
         <v>157.2141674434703</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.86</v>
+        <v>-4.65</v>
       </c>
       <c r="L21" t="n">
-        <v>4.58</v>
+        <v>5.98</v>
       </c>
       <c r="M21" t="n">
         <v>1.64</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H22" t="n">
-        <v>145.1</v>
+        <v>141.5</v>
       </c>
       <c r="I22" t="n">
         <v>144.4358574326039</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.87</v>
+        <v>-10.16</v>
       </c>
       <c r="L22" t="n">
-        <v>8.51</v>
+        <v>11.21</v>
       </c>
       <c r="M22" t="n">
         <v>1.62</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>14.9</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43887</v>
+        <v>43888</v>
       </c>
       <c r="H23" t="n">
-        <v>140.1</v>
+        <v>156.4</v>
       </c>
       <c r="I23" t="n">
         <v>150.3023326190943</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>0.99</v>
+        <v>-10.53</v>
       </c>
       <c r="L23" t="n">
-        <v>9.08</v>
+        <v>14.45</v>
       </c>
       <c r="M23" t="n">
         <v>4.26</v>
       </c>
       <c r="N23" t="n">
-        <v>9.01</v>
+        <v>11.63</v>
       </c>
       <c r="O23" t="n">
         <v>-2.48</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>23.19</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43896</v>
+        <v>43899</v>
       </c>
       <c r="H24" t="n">
-        <v>124.95</v>
+        <v>117.9</v>
       </c>
       <c r="I24" t="n">
         <v>120.1344907505759</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>-20.11</v>
+        <v>-24.62</v>
       </c>
       <c r="L24" t="n">
-        <v>21.68</v>
+        <v>27.11</v>
       </c>
       <c r="M24" t="n">
         <v>8.220000000000001</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>25.27</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43928</v>
+        <v>43929</v>
       </c>
       <c r="H25" t="n">
-        <v>95.7</v>
+        <v>109.1</v>
       </c>
       <c r="I25" t="n">
         <v>107.8823991473924</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>18.83</v>
+        <v>7.46</v>
       </c>
       <c r="L25" t="n">
         <v>4.33</v>
@@ -1866,7 +2165,7 @@
         <v>7.33</v>
       </c>
       <c r="N25" t="n">
-        <v>10.32</v>
+        <v>14</v>
       </c>
       <c r="O25" t="n">
         <v>-5.64</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>30.89</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44074</v>
+        <v>44075</v>
       </c>
       <c r="H26" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="I26" t="n">
         <v>193.5470039984928</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K26" t="n">
-        <v>81.48</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>13.75</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>16.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H27" t="n">
-        <v>150.2</v>
+        <v>157.6</v>
       </c>
       <c r="I27" t="n">
         <v>156.4142333196911</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K27" t="n">
-        <v>21.77</v>
+        <v>17.92</v>
       </c>
       <c r="L27" t="n">
         <v>6.38</v>
@@ -1980,7 +2303,7 @@
         <v>2.32</v>
       </c>
       <c r="N27" t="n">
-        <v>3.79</v>
+        <v>4.93</v>
       </c>
       <c r="O27" t="n">
         <v>-3.03</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44186</v>
+        <v>44187</v>
       </c>
       <c r="H28" t="n">
-        <v>158.35</v>
+        <v>157.75</v>
       </c>
       <c r="I28" t="n">
         <v>157.9619694809863</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>0.48</v>
+        <v>0.1</v>
       </c>
       <c r="L28" t="n">
-        <v>4.66</v>
+        <v>5.74</v>
       </c>
       <c r="M28" t="n">
         <v>0.68</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44196</v>
+        <v>44197</v>
       </c>
       <c r="H29" t="n">
-        <v>170.2</v>
+        <v>174.05</v>
       </c>
       <c r="I29" t="n">
         <v>172.6751322670732</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.89</v>
+        <v>-10.33</v>
       </c>
       <c r="L29" t="n">
-        <v>9.83</v>
+        <v>10.62</v>
       </c>
       <c r="M29" t="n">
         <v>4.48</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.66</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H30" t="n">
-        <v>175.55</v>
+        <v>171</v>
       </c>
       <c r="I30" t="n">
         <v>172.003383562206</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K30" t="n">
-        <v>0.86</v>
+        <v>-1.75</v>
       </c>
       <c r="L30" t="n">
         <v>6.92</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.54</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H31" t="n">
-        <v>169.1</v>
+        <v>179.3</v>
       </c>
       <c r="I31" t="n">
         <v>176.8721072215941</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K31" t="n">
-        <v>1.11</v>
+        <v>-4.85</v>
       </c>
       <c r="L31" t="n">
         <v>7.31</v>
@@ -2208,7 +2579,7 @@
         <v>5.03</v>
       </c>
       <c r="N31" t="n">
-        <v>4.5</v>
+        <v>6.03</v>
       </c>
       <c r="O31" t="n">
         <v>-2.59</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.63</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44418</v>
+        <v>44419</v>
       </c>
       <c r="H32" t="n">
-        <v>191.55</v>
+        <v>187.5</v>
       </c>
       <c r="I32" t="n">
         <v>188.284006809566</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K32" t="n">
-        <v>6.83</v>
+        <v>4.57</v>
       </c>
       <c r="L32" t="n">
         <v>6.69</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>12.49</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44483</v>
+        <v>44487</v>
       </c>
       <c r="H33" t="n">
-        <v>195.5</v>
+        <v>206.6</v>
       </c>
       <c r="I33" t="n">
         <v>201.431244646503</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.27</v>
+        <v>-10.19</v>
       </c>
       <c r="L33" t="n">
-        <v>10.11</v>
+        <v>10.51</v>
       </c>
       <c r="M33" t="n">
         <v>4.04</v>
       </c>
       <c r="N33" t="n">
-        <v>4.69</v>
+        <v>5.68</v>
       </c>
       <c r="O33" t="n">
         <v>-2.11</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.76</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H34" t="n">
-        <v>206</v>
+        <v>194.65</v>
       </c>
       <c r="I34" t="n">
         <v>195.9344319388178</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.29</v>
+        <v>-5.78</v>
       </c>
       <c r="L34" t="n">
-        <v>4.84</v>
+        <v>7.31</v>
       </c>
       <c r="M34" t="n">
         <v>1.46</v>
       </c>
       <c r="N34" t="n">
-        <v>3.47</v>
+        <v>5.51</v>
       </c>
       <c r="O34" t="n">
         <v>5.68</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>17.48</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="H35" t="n">
-        <v>206</v>
+        <v>218.9</v>
       </c>
       <c r="I35" t="n">
         <v>208.9173488138651</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.83</v>
+        <v>-12.46</v>
       </c>
       <c r="L35" t="n">
-        <v>12.77</v>
+        <v>14.26</v>
       </c>
       <c r="M35" t="n">
         <v>2.13</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.99</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44614</v>
+        <v>44615</v>
       </c>
       <c r="H36" t="n">
-        <v>222.2</v>
+        <v>218.45</v>
       </c>
       <c r="I36" t="n">
         <v>220.3428003365951</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K36" t="n">
-        <v>1.51</v>
+        <v>-0.21</v>
       </c>
       <c r="L36" t="n">
         <v>6.19</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.24</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H37" t="n">
-        <v>237.7</v>
+        <v>246.3</v>
       </c>
       <c r="I37" t="n">
         <v>242.0933008600615</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.81</v>
+        <v>-12.75</v>
       </c>
       <c r="L37" t="n">
-        <v>10.09</v>
+        <v>13.3</v>
       </c>
       <c r="M37" t="n">
         <v>3.04</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>15.21</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H38" t="n">
-        <v>357.4</v>
+        <v>342.3</v>
       </c>
       <c r="I38" t="n">
         <v>342.4212499720928</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K38" t="n">
-        <v>45.11</v>
+        <v>38.98</v>
       </c>
       <c r="L38" t="n">
         <v>3.9</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>26.23</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H39" t="n">
-        <v>373.25</v>
+        <v>391.8</v>
       </c>
       <c r="I39" t="n">
         <v>388.6020429682537</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.039999999999999</v>
+        <v>-14.46</v>
       </c>
       <c r="L39" t="n">
         <v>18.73</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>21.1</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44741</v>
+        <v>44742</v>
       </c>
       <c r="H40" t="n">
-        <v>350.1</v>
+        <v>340.6</v>
       </c>
       <c r="I40" t="n">
         <v>344.9180570712123</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>-10.64</v>
+        <v>-13.07</v>
       </c>
       <c r="L40" t="n">
         <v>17.36</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>19.08</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44769</v>
+        <v>44770</v>
       </c>
       <c r="H41" t="n">
-        <v>365.45</v>
+        <v>391.1</v>
       </c>
       <c r="I41" t="n">
         <v>383.7890008937769</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.3</v>
+        <v>-14.83</v>
       </c>
       <c r="L41" t="n">
-        <v>8.460000000000001</v>
+        <v>15.78</v>
       </c>
       <c r="M41" t="n">
         <v>1.44</v>
       </c>
       <c r="N41" t="n">
-        <v>4.27</v>
+        <v>7.02</v>
       </c>
       <c r="O41" t="n">
         <v>-2.71</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44831</v>
+        <v>44832</v>
       </c>
       <c r="H42" t="n">
-        <v>422.4</v>
+        <v>412.4</v>
       </c>
       <c r="I42" t="n">
         <v>416.8155018339703</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>5.45</v>
       </c>
       <c r="L42" t="n">
         <v>6.67</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>14.81</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44854</v>
+        <v>44855</v>
       </c>
       <c r="H43" t="n">
-        <v>460.8</v>
+        <v>478</v>
       </c>
       <c r="I43" t="n">
         <v>473.4810000308677</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.74</v>
+        <v>-15.91</v>
       </c>
       <c r="L43" t="n">
-        <v>15.03</v>
+        <v>16.51</v>
       </c>
       <c r="M43" t="n">
         <v>1.79</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>13.36</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H44" t="n">
-        <v>462</v>
+        <v>438.9</v>
       </c>
       <c r="I44" t="n">
         <v>447.7166913853309</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.35</v>
+        <v>-8.18</v>
       </c>
       <c r="L44" t="n">
-        <v>5.1</v>
+        <v>9.1</v>
       </c>
       <c r="M44" t="n">
         <v>0.65</v>
       </c>
       <c r="N44" t="n">
-        <v>4.03</v>
+        <v>5</v>
       </c>
       <c r="O44" t="n">
         <v>3.73</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>12.27</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44923</v>
+        <v>44924</v>
       </c>
       <c r="H45" t="n">
-        <v>460.5</v>
+        <v>470.2</v>
       </c>
       <c r="I45" t="n">
         <v>466.5600459640963</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.92</v>
+        <v>-7.13</v>
       </c>
       <c r="L45" t="n">
-        <v>6.45</v>
+        <v>7.53</v>
       </c>
       <c r="M45" t="n">
         <v>0.5</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>15</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H46" t="n">
-        <v>444.45</v>
+        <v>425.2</v>
       </c>
       <c r="I46" t="n">
         <v>430.5478581198573</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.48</v>
+        <v>-9.57</v>
       </c>
       <c r="L46" t="n">
-        <v>8.44</v>
+        <v>11.21</v>
       </c>
       <c r="M46" t="n">
-        <v>0.65</v>
+        <v>3.81</v>
       </c>
       <c r="N46" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="O46" t="n">
         <v>2.11</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>14.31</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H47" t="n">
-        <v>400.05</v>
+        <v>450.9</v>
       </c>
       <c r="I47" t="n">
         <v>448.3901920531907</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>5.91</v>
+        <v>-6.04</v>
       </c>
       <c r="L47" t="n">
-        <v>2.3</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>12.71</v>
       </c>
       <c r="O47" t="n">
         <v>-4.33</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>18.34</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45145</v>
+        <v>45146</v>
       </c>
       <c r="H48" t="n">
-        <v>571.2</v>
+        <v>557.5</v>
       </c>
       <c r="I48" t="n">
         <v>558.416607187771</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K48" t="n">
-        <v>26.68</v>
+        <v>23.64</v>
       </c>
       <c r="L48" t="n">
         <v>10.73</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>7</v>
+      </c>
+      <c r="U48" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.62</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="H49" t="n">
-        <v>520.3</v>
+        <v>523.5</v>
       </c>
       <c r="I49" t="n">
         <v>522.3053688570345</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K49" t="n">
-        <v>6.67</v>
+        <v>6.1</v>
       </c>
       <c r="L49" t="n">
         <v>9.81</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H50" t="n">
-        <v>919.3</v>
+        <v>808</v>
       </c>
       <c r="I50" t="n">
         <v>808.519044879456</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K50" t="n">
-        <v>75.61</v>
+        <v>54.35</v>
       </c>
       <c r="L50" t="n">
         <v>1.43</v>
@@ -3291,7 +3890,7 @@
         <v>1.97</v>
       </c>
       <c r="N50" t="n">
-        <v>3.87</v>
+        <v>12.11</v>
       </c>
       <c r="O50" t="n">
         <v>0.62</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>25.79</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45404</v>
+        <v>45405</v>
       </c>
       <c r="H51" t="n">
-        <v>922.1</v>
+        <v>961.55</v>
       </c>
       <c r="I51" t="n">
         <v>936.3176438593621</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K51" t="n">
-        <v>-14.12</v>
+        <v>-19</v>
       </c>
       <c r="L51" t="n">
         <v>22.82</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>13.03</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H52" t="n">
-        <v>1436.85</v>
+        <v>1305.25</v>
       </c>
       <c r="I52" t="n">
         <v>1308.050304643817</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K52" t="n">
-        <v>49.43</v>
+        <v>35.74</v>
       </c>
       <c r="L52" t="n">
         <v>6.11</v>
       </c>
       <c r="M52" t="n">
-        <v>1.04</v>
+        <v>4.53</v>
       </c>
       <c r="N52" t="n">
         <v>10</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>28.75</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45476</v>
+        <v>45477</v>
       </c>
       <c r="H53" t="n">
-        <v>1633.8</v>
+        <v>1683.9</v>
       </c>
       <c r="I53" t="n">
         <v>1680.490003238509</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K53" t="n">
-        <v>-25.17</v>
+        <v>-29.01</v>
       </c>
       <c r="L53" t="n">
-        <v>28.4</v>
+        <v>31.39</v>
       </c>
       <c r="M53" t="n">
         <v>1.92</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>14.34</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H54" t="n">
-        <v>1546.45</v>
+        <v>1467.75</v>
       </c>
       <c r="I54" t="n">
         <v>1473.99291312789</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.16</v>
+        <v>-12.84</v>
       </c>
       <c r="L54" t="n">
-        <v>8.94</v>
+        <v>13.18</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="N54" t="n">
-        <v>3.46</v>
+        <v>5.09</v>
       </c>
       <c r="O54" t="n">
         <v>3.07</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>19.23</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H55" t="n">
-        <v>1032.1</v>
+        <v>1116.75</v>
       </c>
       <c r="I55" t="n">
         <v>1081.508490810886</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K55" t="n">
-        <v>29.68</v>
+        <v>23.91</v>
       </c>
       <c r="L55" t="n">
         <v>5.94</v>
@@ -3576,7 +4235,7 @@
         <v>3.17</v>
       </c>
       <c r="N55" t="n">
-        <v>6.28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O55" t="n">
         <v>-5.09</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>18.61</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H56" t="n">
-        <v>1199.95</v>
+        <v>1108.05</v>
       </c>
       <c r="I56" t="n">
         <v>1149.598104001959</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K56" t="n">
-        <v>7.45</v>
+        <v>-0.78</v>
       </c>
       <c r="L56" t="n">
         <v>7.57</v>
@@ -3633,7 +4304,7 @@
         <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>2.86</v>
+        <v>7.66</v>
       </c>
       <c r="O56" t="n">
         <v>8.199999999999999</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>18.43</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H57" t="n">
-        <v>1201.45</v>
+        <v>1276.25</v>
       </c>
       <c r="I57" t="n">
         <v>1275.956187795824</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.43</v>
+        <v>-15.18</v>
       </c>
       <c r="L57" t="n">
-        <v>10.92</v>
+        <v>16.38</v>
       </c>
       <c r="M57" t="n">
         <v>0.76</v>
       </c>
       <c r="N57" t="n">
-        <v>5.95</v>
+        <v>6.23</v>
       </c>
       <c r="O57" t="n">
         <v>-7.66</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>17.43</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H58" t="n">
-        <v>1166.7</v>
+        <v>1102.55</v>
       </c>
       <c r="I58" t="n">
         <v>1124.345313014429</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.58</v>
+        <v>-13.61</v>
       </c>
       <c r="L58" t="n">
         <v>17.88</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>23.76</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H59" t="n">
-        <v>1126.8</v>
+        <v>1198</v>
       </c>
       <c r="I59" t="n">
         <v>1146.029457504517</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.2</v>
+        <v>-8.66</v>
       </c>
       <c r="L59" t="n">
-        <v>7.68</v>
+        <v>10.93</v>
       </c>
       <c r="M59" t="n">
         <v>1.2</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>16.55</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="H60" t="n">
-        <v>1802</v>
+        <v>1742.9</v>
       </c>
       <c r="I60" t="n">
         <v>1798.970523937757</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K60" t="n">
-        <v>50.42</v>
+        <v>45.48</v>
       </c>
       <c r="L60" t="n">
         <v>5.84</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>12.06</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H61" t="n">
-        <v>1481.6</v>
+        <v>1566.5</v>
       </c>
       <c r="I61" t="n">
         <v>1558.929733495584</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" t="n">
-        <v>14.99</v>
+        <v>10.12</v>
       </c>
       <c r="L61" t="n">
         <v>4.13</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.83</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H62" t="n">
-        <v>1555.9</v>
+        <v>1497.8</v>
       </c>
       <c r="I62" t="n">
         <v>1499.919684766951</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.68</v>
+        <v>-4.39</v>
       </c>
       <c r="L62" t="n">
         <v>5.42</v>
@@ -3975,7 +4718,7 @@
         <v>0.66</v>
       </c>
       <c r="N62" t="n">
-        <v>1.98</v>
+        <v>3.73</v>
       </c>
       <c r="O62" t="n">
         <v>5.73</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>11.57</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="H63" t="n">
-        <v>1517.9</v>
+        <v>1613.8</v>
       </c>
       <c r="I63" t="n">
         <v>1557.220997159429</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.34</v>
+        <v>-7.74</v>
       </c>
       <c r="L63" t="n">
-        <v>5.4</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>2.98</v>
+        <v>5.47</v>
       </c>
       <c r="N63" t="n">
-        <v>4.61</v>
+        <v>6.32</v>
       </c>
       <c r="O63" t="n">
         <v>-3.73</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H64" t="n">
-        <v>1512.5</v>
+        <v>1423.1</v>
       </c>
       <c r="I64" t="n">
         <v>1460.000649387329</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.28</v>
+        <v>-11.82</v>
       </c>
       <c r="L64" t="n">
-        <v>9.52</v>
+        <v>12.01</v>
       </c>
       <c r="M64" t="n">
-        <v>0.97</v>
+        <v>1.16</v>
       </c>
       <c r="N64" t="n">
-        <v>2.85</v>
+        <v>5.91</v>
       </c>
       <c r="O64" t="n">
         <v>6.32</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>12.68</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="H65" t="n">
-        <v>1431.4</v>
+        <v>1481.2</v>
       </c>
       <c r="I65" t="n">
         <v>1455.27102492115</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.58</v>
+        <v>-4.08</v>
       </c>
       <c r="L65" t="n">
         <v>5.8</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>10.37</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H66" t="n">
-        <v>1453.1</v>
+        <v>1419.2</v>
       </c>
       <c r="I66" t="n">
         <v>1421.145907404673</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.9</v>
+        <v>-4.19</v>
       </c>
       <c r="L66" t="n">
-        <v>3.68</v>
+        <v>4.74</v>
       </c>
       <c r="M66" t="n">
         <v>0.82</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>10.64</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H67" t="n">
-        <v>1469.4</v>
+        <v>1570</v>
       </c>
       <c r="I67" t="n">
         <v>1564.822900533635</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.54</v>
+        <v>-10.63</v>
       </c>
       <c r="L67" t="n">
-        <v>4.64</v>
+        <v>11.01</v>
       </c>
       <c r="M67" t="n">
         <v>0.5</v>
       </c>
       <c r="N67" t="n">
-        <v>4.36</v>
+        <v>6.85</v>
       </c>
       <c r="O67" t="n">
         <v>-2.33</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>13.27</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H68" t="n">
-        <v>1538.2</v>
+        <v>1384.1</v>
       </c>
       <c r="I68" t="n">
         <v>1389.830855510981</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.03</v>
+        <v>-11.84</v>
       </c>
       <c r="L68" t="n">
-        <v>6.22</v>
+        <v>12.74</v>
       </c>
       <c r="M68" t="n">
-        <v>0.37</v>
+        <v>2.16</v>
       </c>
       <c r="N68" t="n">
-        <v>2.5</v>
+        <v>10.02</v>
       </c>
       <c r="O68" t="n">
         <v>6.85</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>19.11</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H69" t="n">
-        <v>1235.9</v>
+        <v>1291.4</v>
       </c>
       <c r="I69" t="n">
         <v>1283.691977599457</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K69" t="n">
-        <v>10.71</v>
+        <v>6.7</v>
       </c>
       <c r="L69" t="n">
         <v>9.960000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>3.51</v>
+        <v>4.77</v>
       </c>
       <c r="N69" t="n">
         <v>9.779999999999999</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>14.88</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H70" t="n">
-        <v>1325.4</v>
+        <v>1309.2</v>
       </c>
       <c r="I70" t="n">
         <v>1322.845264149391</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K70" t="n">
-        <v>2.63</v>
+        <v>1.38</v>
       </c>
       <c r="L70" t="n">
         <v>2.9</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>10.32</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H71" t="n">
-        <v>1236.7</v>
+        <v>1309.8</v>
       </c>
       <c r="I71" t="n">
         <v>1286.845285220977</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K71" t="n">
-        <v>5.54</v>
+        <v>-0.05</v>
       </c>
       <c r="L71" t="n">
         <v>2.96</v>
@@ -4488,7 +5339,7 @@
         <v>1.53</v>
       </c>
       <c r="N71" t="n">
-        <v>3.44</v>
+        <v>5.91</v>
       </c>
       <c r="O71" t="n">
         <v>-1.22</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>12.43</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="H72" t="n">
-        <v>1302.8</v>
+        <v>1277.8</v>
       </c>
       <c r="I72" t="n">
         <v>1288.350480919114</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.53</v>
+        <v>-2.44</v>
       </c>
       <c r="L72" t="n">
         <v>5.93</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>10.31</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H73" t="n">
-        <v>1307.6</v>
+        <v>1340</v>
       </c>
       <c r="I73" t="n">
         <v>1334.840213833779</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.33</v>
+        <v>-4.87</v>
       </c>
       <c r="L73" t="n">
-        <v>3.24</v>
+        <v>4.87</v>
       </c>
       <c r="M73" t="n">
         <v>0.61</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>8.48</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H74" t="n">
-        <v>1306</v>
+        <v>1275</v>
       </c>
       <c r="I74" t="n">
         <v>1278.516242464445</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.54</v>
+        <v>-4.85</v>
       </c>
       <c r="L74" t="n">
-        <v>2.91</v>
+        <v>5.48</v>
       </c>
       <c r="M74" t="n">
         <v>0.75</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>40</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8385,7 +9292,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -8395,7 +9302,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -8405,7 +9312,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -8415,7 +9322,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8425,7 +9332,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -8435,7 +9342,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -8445,7 +9352,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -8455,7 +9362,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -8465,7 +9372,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50.7</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="14">
@@ -8475,7 +9382,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.04</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="15">
@@ -8485,7 +9392,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.85</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="16">
@@ -8495,7 +9402,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.15</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="17">
@@ -8505,7 +9412,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>81.48</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -8515,7 +9422,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="19">
@@ -8525,7 +9432,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.34</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="20">
@@ -8535,7 +9442,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.3</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="21">
@@ -8545,7 +9452,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28.4</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="22">
@@ -8555,7 +9462,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
@@ -8565,7 +9472,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -8575,7 +9482,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="25">
@@ -8595,7 +9502,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.07</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="27">
@@ -8605,7 +9512,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.34</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="28">
@@ -8615,7 +9522,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
